--- a/data/daily/2026-10/2026-10-26.xlsx
+++ b/data/daily/2026-10/2026-10-26.xlsx
@@ -1165,7 +1165,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1190,10 +1190,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1215,7 +1215,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1240,7 +1240,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1265,10 +1265,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1290,10 +1290,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1315,10 +1315,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1340,7 +1340,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1361,31 +1361,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1393,7 +1368,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1418,12 +1393,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1443,7 +1418,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1468,7 +1443,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1493,12 +1468,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1518,12 +1493,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1543,12 +1518,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1556,31 +1531,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1601,11 +1551,11 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2007,7 +1957,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2027,29 +1977,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008175849_168a24e2374741c7ba9fef1fb068d098.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026112036_e3a7e53364444920a21456d555f6b17c.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16351</v>
+        <v>16352</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 고급스러운 패키지와 알찬 구성으로 선물 시 받는 사람의 만족도가 높음</t>
+          <t>우수한 피로 회복 효과 — 피로가 풀리고 일상에 활력 및 에너지를 더해줌.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 개선 — 섭취 후 피로가 풀어지고 일상생활에 활력이 생김</t>
+          <t>고급스러운 선물용 패키지 — 알찬 구성과 깔끔한 상자 패키지로 선물용으로 적합함.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>원산지 표시 위치 아쉬움 — 원산지가 표지면 앞이나 뒤에 명확히 표기되었으면 하는 아쉬움이 있음</t>
+          <t>원산지 표시 위치 아쉬움 — 표지면 앞뒤에 원산지가 더 정확히 표시되면 좋을 것 같음.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2097,15 +2047,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>세련된 패키지와 선물 만족 — 패키지가 세련되어 선물받았을 때 기분이 좋고 만족스러움</t>
+          <t>간편한 섭취 편의성 — 액상과 정제가 함께 있어 언제 어디서나 간편하게 복용 가능함.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 복용과 피로 회복 — 알약과 액상이 함께 구성되어 복용이 간편하며 야근 시 피로 회복에 효과적임</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>피로 회복 및 활력 증진 — 야근이나 피로감이 쌓였을 때 힘이 나고 효과적임.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>세련된 선물용 패키지 — 패키지가 깔끔하고 세련되어 생일이나 응원 선물로 만족스러움.</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2121,7 +2075,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>'2입 증정' "독일 명품 비타민" 오쏘몰 이뮨 멀티비타민&amp;미네랄 30+2입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2131,7 +2085,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>105,000원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2141,7 +2095,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008180121_22a6a37ed12f40d38d9092445158a591.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026112217_85fa59d63699475cb038fe852134bd56.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -2152,15 +2106,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 체력 증진 효과 — 섭취 시 속이 편안하고 체력이 달릴 때 확실하게 에너지를 채워줌</t>
+          <t>확실한 체력 충전 효과 — 지치거나 체력이 떨어졌을 때 먹으면 확실하게 힘이 남.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진한 액상 농도와 품질 — 타 액상 제품 대비 농도가 찐하고 비싼 만큼 선물 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>진한 액상과 편안한 속 — 타 제품 대비 액상 농도가 진하며 섭취 후 속이 편안함.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>높은 선물 만족도 — 구성이 고급스럽고 인지도가 높아 선물 시 만족도가 큼.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2203,25 +2161,29 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6535</v>
+        <v>6536</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤하고 적당히 쫄깃하여 아이나 어른 모두 간식처럼 먹기 좋음</t>
+          <t>맛있는 구미 제형의 편의성 — 새콤달콤하고 쫄깃하여 거부감 없이 쉽게 비타민을 챙겨 먹을 수 있음.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 영양 섭취 — 바쁜 아침이나 출근 시 물 없이 씹어서 간편하게 영양을 챙길 수 있음</t>
+          <t>적당한 식감과 기분 전환 — 과하게 달지 않고 씹는 맛이 있어 간식처럼 즐기기 좋음.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>포장 개봉의 어려움 — 제품 개봉 시 잘 뜯어지지 않아 불편하다는 의견이 있음</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>개봉 시 포장의 불편함 — 포장이 잘 뜯어지지 않아 개봉할 때 불편함이 있음.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>강한 간식 제형의 느낌 — 너무 젤리나 어린이 비타민 같아 영양제 느낌이 다소 적음.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
@@ -2266,15 +2228,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로 회복에 아주 좋으며 환절기 선물이나 일상 비타민으로 적합함</t>
+          <t>뛰어난 피로 회복 효과 — 피로 회복에 효과적이며 환절기나 힘든 시기를 버티는 데 도움 됨.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성과 편의성 — 휴대하기 편하고 먹기도 편리하여 챙겨 먹기 용이함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>편리한 휴대성 및 섭취법 — 휴대하기 쉽고 간편하게 섭취할 수 있어 매일 챙기기 좋음.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>알찬 선물용 상품 구성 — 구성과 배송이 훌륭하여 주변 사람에게 선물하기에 적절함.</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2321,16 +2287,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 깔끔하고 고급스러운 포장에 증정품이 포함되어 선물용으로 매우 좋음</t>
+          <t>상큼하고 맛있는 풍미 — 기존 비타민 대비 신맛이 적고 단맛이 감돌아 마시기 편함.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>흥미로운 섭취 방식과 맛 — 버튼을 눌러 분말과 액상을 섞는 방식이 재밌고 신맛이 적으며 단맛이 나 상큼함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>독특한 섭취 방식과 감성 — 버튼을 눌러 분말과 액상을 섞는 재미가 있고 패키지가 고급스러움.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>추가 증정 혜택 및 활력 — 1입 추가 증정 구성이 알차며 체력 보충 및 활력 충전에 효과적임.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>음용 방식 미숙지 시 실패 — 분말과 액상을 섞는 방식이라 설명서를 읽지 않으면 음용 시 실패할 수 있음.</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2376,15 +2350,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 마시는 액상 형태 — 마시는 액상 제형으로 섭취가 간편하여 자주 찾게 됨</t>
+          <t>간편한 액상형 섭취 제형 — 액상 제형으로 이루어져 물 없이도 쉽게 마시기 편함.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 충전 — 아침 출근 전이나 체력이 떨어질 때 먹으면 기운이 나고 피로가 해소됨</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>아침 피로 회복과 활력 — 피곤한 아침에 복용 시 기운이 나며 하루를 힘차게 시작할 수 있음.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 알찬 선물 — 배송이 빠르고 센스 있는 구성이라 영양제 선물로 적합함.</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2400,7 +2378,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>성별 맞춤 설계 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2420,29 +2398,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026112443_35b6bcb5a63247d99af28ae3f95f1a7f.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>확실한 활력 증진 효과 — 바쁘고 힘들 때 먹으면 활력이 확실히 돋아 직장인 필수템으로 추천됨</t>
+          <t>확실한 활력 충전 효과 — 바쁘거나 피곤할 때 먹으면 체력과 활력이 눈에 띄게 개선됨.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>유용한 구성과 선물 만족 — 먹기 편하고 배송 상태가 양호하며 누구에게나 유용한 선물이 됨</t>
+          <t>편리한 섭취 및 휴대성 — 개별 포장 형태로 어디서나 편리하게 챙겨 먹기 좋음.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>호불호 갈리는 맛 — 오렌지 맛 감기약 같은 맛이 나 호불호가 갈릴 수 있음</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 약이나 감기약 느낌이 나서 맛 자체는 아쉬움.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2490,18 +2468,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>고함량 비타민C 섭취 — 3000mg 고함량 비타민C로 피로 체감 시 리프레쉬 효과를 받음</t>
+          <t>3000mg 고함량 비타민 — 고함량 구성으로 피로감 완화 및 리프레쉬 효과가 뛰어남.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>높은 휴대성과 빠른 배송 — 가방에 넣어 다니며 챙겨 먹기 좋고 배송이 매우 빠름</t>
+          <t>빠른 배송과 뛰어난 휴대성 — 배송이 신속하며 가방에 가지고 다니며 챙겨 먹기 편함.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>시절하고 강한 맛 — 분말 맛이 매우 셔서 물 없이 섭취하기에 다소 부담스러움</t>
+          <t>강한 신맛으로 인한 부담 — 신맛이 매우 강해 물 없이 먹기 힘들며 입맛에 따라 거부감이 들 수 있음.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2549,18 +2527,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>한 포 개별 포장의 편의성 — 24종 기능성을 한 포에 담아 개별 포장되어 있어 깔끔하고 간편함</t>
+          <t>한 포로 끝내는 종합 영양 — 24종 기능성을 한 포에 담아 개별 포장으로 편리하게 챙길 수 있음.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 패키징이 고급스러우며 일주일 정도 섭취 시 힘이 나는 것을 느낌</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>고급스러운 패키지 디자인 — 포장이 깔끔하고 고급스러워 감동적인 선물용으로 적합함.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>체력 증진 및 피로 개선 — 꾸준히 섭취 시 활력이 돋고 힘이 나는 효과를 체감함.</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 — 동봉된 사은품의 품질이 저가 판매점 제품이라 다소 아쉬움</t>
+          <t>사은품의 아쉬운 품질 — 제공된 사은품이 다이소 판매 상품이라 다소 아쉬움.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2577,7 +2559,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로차진액 스틱 5포 증정</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2597,26 +2579,30 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021101500_a33c07ee9dfe4879b427c57a18d9ce91.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026141404_b1c5e3127aad4b51b5e3d0ac9e906be1.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>푸짐한 증정품 혜택 — 추가 증정포와 단백질바, 파로칩 등 후한 사은품 구성이 만족스러움</t>
+          <t>속 편한 소화 개선 효과 — 섭취 후 더부룩함이 줄어들고 속이 편안해지는 효능이 탁월함.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 맛 — 할인가로 구매 시 매우 저렴하며 맛도 좋아 장기간 꾸준히 재구매함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>거부감 없는 고소한 맛 — 효소 특유의 거부감 없이 맛있게 먹을 수 있음.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>풍성한 증정품과 가성비 — 톡딜 이벤트 시 저렴하며 추가 증정품 구성이 매우 풍성함.</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -2663,15 +2649,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리가 덜 아프고 숙취 완화에 효과적임</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리 아픔과 속 더부룩함이 크게 줄어듦.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>휴대 및 섭취의 용이성 — 스틱 액상 형태라 소지하기 좋고 거부감 없는 맛으로 물 없이 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>휴대가 간편한 액상 스틱 — 액상 스틱 형태로 물 없이도 바로 마실 수 있으며 휴대하기 편함.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>거부감 없는 상큼한 맛 — 환 제형과 달리 맛이 텁텁하지 않고 맛있어서 편하게 먹을 수 있음.</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2718,15 +2708,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>부드러운 식감과 뛰어난 맛 — 살이 부드럽고 퍽퍽하지 않으며 다양한 맛으로 구성되어 질리지 않음</t>
+          <t>부드러운 식감과 우수한 맛 — 닭가슴살이 퍽퍽하지 않고 부드러우며 감칠맛이 뛰어남.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>간편한 식단 관리 — 다이어트 식단 및 간식용으로 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>다채롭고 질리지 않는 맛 — 옵션과 맛의 종류가 다채로워 매일 질리지 않고 먹을 수 있음.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>식단 관리용 간식 활용 — 칼로리 부담 없이 식단 관리나 간식용으로 활용하기 좋음.</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2742,7 +2736,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2762,7 +2756,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014082110_1396a6238ec2436a8ec1f9ee6f6c2055.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026140618_d8294b0175c344218da6d62160aa60a0.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2773,16 +2767,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>고소한 맛과 편안한 소화 — 미숫가루처럼 고소한 맛이 나며 식후 속을 편안하게 해줌</t>
+          <t>속 편한 소화 개선 효능 — 더부룩할 때 먹으면 속이 편안해지고 소화에 도움을 줌.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>정성스러운 선물 포장 — 패키지가 고급스럽고 견과류 바 등 사은품 혜택이 좋아 선물용으로 추천함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>고소한 미숫가루 풍미 — 텁텁함 없이 미숫가루나 곡물처럼 고소해서 먹기 부담 없음.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>고급 포장과 알찬 사은품 — 패키지가 고급스럽고 견과류 바 등 사은품 구성이 알참.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>기프티콘 확인의 난해함 — 제공되는 기프티콘 수령 및 확인 방법에 대한 안내가 다소 미흡함.</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -2828,15 +2830,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 조리 편의 — 닭가슴살이 촉촉하며 전자레인지로 간편하게 데워 먹기 좋음</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살임에도 퍽퍽하지 않고 촉촉한 식감을 유지함.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>다양한 맛과 착한 가격 — 맛의 종류가 다양하여 질리지 않고 식단 관리할 수 있으며 가격이 저렴함</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>간편한 조리 및 활용성 — 전자레인지에 간편히 데워 식사 대용이나 반찬으로 먹기 좋음.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>다양하고 맛있는 양념 맛 — 떡볶이맛 등 다채로운 양념이 더해져 질리지 않고 식단 관리가 가능함.</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2883,15 +2889,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>기획 굿즈와 알찬 구성 — 포토카드 및 엽서 굿즈와 증정 단백질바 구성이 훌륭함</t>
+          <t>포토카드 및 굿즈 구성 — 최애 멤버 포토카드와 엽서 등이 포함되어 만족도가 높음.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 효과 — 쿠키앤크림, 소다 맛 등 맛이 우수하여 과식 후 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>맛있는 디저트 맛 효소 — 쿠키앤크림, 소다아이스크림 등 특색 있고 맛있는 맛으로 구성됨.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>풍성하고 알찬 추가 증정 — 함께 증정되는 단백질바 맛이 좋고 간식으로 활용하기 좋음.</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2938,18 +2948,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 식감 — 계란 비린 맛이 전혀 없고 구운란처럼 맛과 식감이 뛰어남</t>
+          <t>노른자 없는 100% 흰자 — 노른자가 없어 퍽퍽하지 않고 칼로리 부담 없이 단백질만 챙길 수 있음.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>노른자 없는 단백질 섭취 — 흰자만 들어있어 퍽퍽하지 않고 껍질을 까는 번거로움 없이 간편하게 단백질 보충 가능함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>계란 비린내 없는 맛 — 비린 맛이 전혀 없고 구운란처럼 적당히 짭조름하여 맛있음.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>손쉬운 섭취의 간편식 — 껍질을 깔 필요가 없어 장소 구애 없이 전자레인지로 간편하게 먹음.</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>아쉬운 박스 포장 상태 — 배송받은 포장 박스가 깨끗하지 않고 재활용된 느낌이 듦</t>
+          <t>단일 맛 구성의 아쉬움 — 맛 혼합 구성 옵션이 부족하고 배송 박스 위생 상태가 다소 아쉬움.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2966,7 +2980,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2997,23 +3011,23 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>다채로운 맛과 가성비 — 떡볶이맛 등 다양한 맛으로 구성되어 가성비 있게 구매 가능함</t>
+          <t>맛있고 다채로운 양념 맛 — 떡볶이맛 등 양념이 다양하여 질리지 않고 맛있게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>실용적인 사은품 가방 — 증정품으로 제공되는 보냉 가방의 디자인과 실용성이 우수함</t>
+          <t>실용적인 보냉 가방 증정 — 함께 제공되는 보냉가방의 디자인과 활용도가 뛰어남.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>누락 및 오배송 문제 — 상품 수량이 안 맞거나 사전에 없이 임의 대체 품목으로 배송됨</t>
+          <t>누락 오배송 시 느린 대응 — 구성품 수량이 맞지 않거나 대체품으로 누락되어 CS 응대가 지연됨.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>강한 간과 해동 아쉬움 — 제품의 간이 세게 느껴지거나 배송 시 약간 녹아서 오는 점이 아쉬움</t>
+          <t>강한 간과 구성의 아쉬움 — 자극적인 양념 간이 강하고 가격 대비 가성비가 다소 저렴한 구성임.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -3021,7 +3035,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3029,46 +3043,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>허닭</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/1115219</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021173253_c716df66353b42e9b0e73e5db0962008.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>761</v>
+        <v>1929</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 플리츠백 선물 포장이 예쁘고 고급스러워 개봉 시 기분이 좋음</t>
+          <t>다채로운 20종 상품 구성 — 식단이 질리지 않도록 다양한 닭가슴살 종류로 구성됨.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>섭취 편의성과 맛 — 앰플 형태로 먹기 편하고 맛이 우수하여 피부 건강 관리에 용이함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함이 없이 부드럽고 촉촉하여 먹기 편함.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>전자레인지 전용 용기 제공 — 전용 용기가 포함되어 간편하게 조리하여 데워 먹기 좋음.</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3076,7 +3094,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3084,46 +3102,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>허닭</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/1115219</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20250905115609_5450753e060a41638bfa377ba344c7c2.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026100840_629c26bcd34b4b2c9b2b3dbda7297fd4.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1929</v>
+        <v>761</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다채로운 20종 구성 — 다양한 종류로 구성되어 질리지 않고 매일 다이어트 식단으로 즐기기 좋음</t>
+          <t>화려하고 고급스러운 포장 — 오간자 에디션 및 플리츠백 구성으로 선물의 격을 높여줌.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 편의성 — 닭가슴살이 부드럽고 촉촉하며 전자레인지 전용 용기를 제공해 편함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>맛있고 간편한 앰플 제형 — 비린 맛 없이 맛이 상큼하며 하루 한 병 간편하게 마실 수 있음.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>피부 수분 및 활력 개선 — 꾸준히 섭취 시 피부가 촉촉해지고 피로감이 완화되는 효과를 느낌.</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3353,7 +3375,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 8입(7+1) - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3363,7 +3385,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>'2입 증정' "독일 명품 비타민" 오쏘몰 이뮨 멀티비타민&amp;미네랄 30+2입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3388,7 +3410,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>성별 맞춤 설계 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3446,7 +3468,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16351</v>
+        <v>16352</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15690</v>
@@ -3455,7 +3477,7 @@
         <v>3425</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6535</v>
+        <v>6536</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>834</v>
@@ -3467,7 +3489,7 @@
         <v>8765</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>993</v>
@@ -3476,7 +3498,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -3484,66 +3506,72 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 고급스러운 패키지와 알찬 구성으로 선물 시 받는 사람의 만족도가 높음
-피로 회복 및 활력 개선 — 섭취 후 피로가 풀어지고 일상생활에 활력이 생김</t>
+          <t>우수한 피로 회복 효과 — 피로가 풀리고 일상에 활력 및 에너지를 더해줌.
+고급스러운 선물용 패키지 — 알찬 구성과 깔끔한 상자 패키지로 선물용으로 적합함.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>세련된 패키지와 선물 만족 — 패키지가 세련되어 선물받았을 때 기분이 좋고 만족스러움
-간편한 복용과 피로 회복 — 알약과 액상이 함께 구성되어 복용이 간편하며 야근 시 피로 회복에 효과적임</t>
+          <t>간편한 섭취 편의성 — 액상과 정제가 함께 있어 언제 어디서나 간편하게 복용 가능함.
+피로 회복 및 활력 증진 — 야근이나 피로감이 쌓였을 때 힘이 나고 효과적임.
+세련된 선물용 패키지 — 패키지가 깔끔하고 세련되어 생일이나 응원 선물로 만족스러움.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 체력 증진 효과 — 섭취 시 속이 편안하고 체력이 달릴 때 확실하게 에너지를 채워줌
-진한 액상 농도와 품질 — 타 액상 제품 대비 농도가 찐하고 비싼 만큼 선물 만족도가 높음</t>
+          <t>확실한 체력 충전 효과 — 지치거나 체력이 떨어졌을 때 먹으면 확실하게 힘이 남.
+진한 액상과 편안한 속 — 타 제품 대비 액상 농도가 진하며 섭취 후 속이 편안함.
+높은 선물 만족도 — 구성이 고급스럽고 인지도가 높아 선물 시 만족도가 큼.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 새콤달콤하고 적당히 쫄깃하여 아이나 어른 모두 간식처럼 먹기 좋음
-간편한 영양 섭취 — 바쁜 아침이나 출근 시 물 없이 씹어서 간편하게 영양을 챙길 수 있음</t>
+          <t>맛있는 구미 제형의 편의성 — 새콤달콤하고 쫄깃하여 거부감 없이 쉽게 비타민을 챙겨 먹을 수 있음.
+적당한 식감과 기분 전환 — 과하게 달지 않고 씹는 맛이 있어 간식처럼 즐기기 좋음.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로 회복에 아주 좋으며 환절기 선물이나 일상 비타민으로 적합함
-뛰어난 휴대성과 편의성 — 휴대하기 편하고 먹기도 편리하여 챙겨 먹기 용이함</t>
+          <t>뛰어난 피로 회복 효과 — 피로 회복에 효과적이며 환절기나 힘든 시기를 버티는 데 도움 됨.
+편리한 휴대성 및 섭취법 — 휴대하기 쉽고 간편하게 섭취할 수 있어 매일 챙기기 좋음.
+알찬 선물용 상품 구성 — 구성과 배송이 훌륭하여 주변 사람에게 선물하기에 적절함.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 깔끔하고 고급스러운 포장에 증정품이 포함되어 선물용으로 매우 좋음
-흥미로운 섭취 방식과 맛 — 버튼을 눌러 분말과 액상을 섞는 방식이 재밌고 신맛이 적으며 단맛이 나 상큼함</t>
+          <t>상큼하고 맛있는 풍미 — 기존 비타민 대비 신맛이 적고 단맛이 감돌아 마시기 편함.
+독특한 섭취 방식과 감성 — 버튼을 눌러 분말과 액상을 섞는 재미가 있고 패키지가 고급스러움.
+추가 증정 혜택 및 활력 — 1입 추가 증정 구성이 알차며 체력 보충 및 활력 충전에 효과적임.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 마시는 액상 형태 — 마시는 액상 제형으로 섭취가 간편하여 자주 찾게 됨
-피로 개선 및 활력 충전 — 아침 출근 전이나 체력이 떨어질 때 먹으면 기운이 나고 피로가 해소됨</t>
+          <t>간편한 액상형 섭취 제형 — 액상 제형으로 이루어져 물 없이도 쉽게 마시기 편함.
+아침 피로 회복과 활력 — 피곤한 아침에 복용 시 기운이 나며 하루를 힘차게 시작할 수 있음.
+빠른 배송 및 알찬 선물 — 배송이 빠르고 센스 있는 구성이라 영양제 선물로 적합함.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 증진 효과 — 바쁘고 힘들 때 먹으면 활력이 확실히 돋아 직장인 필수템으로 추천됨
-유용한 구성과 선물 만족 — 먹기 편하고 배송 상태가 양호하며 누구에게나 유용한 선물이 됨</t>
+          <t>확실한 활력 충전 효과 — 바쁘거나 피곤할 때 먹으면 체력과 활력이 눈에 띄게 개선됨.
+편리한 섭취 및 휴대성 — 개별 포장 형태로 어디서나 편리하게 챙겨 먹기 좋음.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 섭취 — 3000mg 고함량 비타민C로 피로 체감 시 리프레쉬 효과를 받음
-높은 휴대성과 빠른 배송 — 가방에 넣어 다니며 챙겨 먹기 좋고 배송이 매우 빠름</t>
+          <t>3000mg 고함량 비타민 — 고함량 구성으로 피로감 완화 및 리프레쉬 효과가 뛰어남.
+빠른 배송과 뛰어난 휴대성 — 배송이 신속하며 가방에 가지고 다니며 챙겨 먹기 편함.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>한 포 개별 포장의 편의성 — 24종 기능성을 한 포에 담아 개별 포장되어 있어 깔끔하고 간편함
-고급스러운 선물 포장 — 패키징이 고급스러우며 일주일 정도 섭취 시 힘이 나는 것을 느낌</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>한 포로 끝내는 종합 영양 — 24종 기능성을 한 포에 담아 개별 포장으로 편리하게 챙길 수 있음.
+고급스러운 패키지 디자인 — 포장이 깔끔하고 고급스러워 감동적인 선물용으로 적합함.
+체력 증진 및 피로 개선 — 꾸준히 섭취 시 활력이 돋고 힘이 나는 효과를 체감함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3551,32 +3579,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>원산지 표시 위치 아쉬움 — 원산지가 표지면 앞이나 뒤에 명확히 표기되었으면 하는 아쉬움이 있음</t>
+          <t>원산지 표시 위치 아쉬움 — 표지면 앞뒤에 원산지가 더 정확히 표시되면 좋을 것 같음.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 어려움 — 제품 개봉 시 잘 뜯어지지 않아 불편하다는 의견이 있음</t>
+          <t>개봉 시 포장의 불편함 — 포장이 잘 뜯어지지 않아 개봉할 때 불편함이 있음.
+강한 간식 제형의 느낌 — 너무 젤리나 어린이 비타민 같아 영양제 느낌이 다소 적음.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>음용 방식 미숙지 시 실패 — 분말과 액상을 섞는 방식이라 설명서를 읽지 않으면 음용 시 실패할 수 있음.</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 맛 — 오렌지 맛 감기약 같은 맛이 나 호불호가 갈릴 수 있음</t>
+          <t>호불호 갈리는 약 맛 — 오렌지 맛 약이나 감기약 느낌이 나서 맛 자체는 아쉬움.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>시절하고 강한 맛 — 분말 맛이 매우 셔서 물 없이 섭취하기에 다소 부담스러움</t>
+          <t>강한 신맛으로 인한 부담 — 신맛이 매우 강해 물 없이 먹기 힘들며 입맛에 따라 거부감이 들 수 있음.</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 — 동봉된 사은품의 품질이 저가 판매점 제품이라 다소 아쉬움</t>
+          <t>사은품의 아쉬운 품질 — 제공된 사은품이 다이소 판매 상품이라 다소 아쉬움.</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3631,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>105,000원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3816,12 +3849,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3906,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>허닭</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>허닭</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3923,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로차진액 스틱 5포 증정</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3905,7 +3938,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)+9포+견과류바 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) + 9포 추가증정</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3925,17 +3958,17 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분+앰플 2입 추가 증정</t>
+          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>BEST다모였닭 허닭 닭가슴살 다양하게 즐기기 20종 패키지</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4016,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>112</v>
@@ -4007,13 +4040,13 @@
         <v>162</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>1929</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>761</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4021,62 +4054,71 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>푸짐한 증정품 혜택 — 추가 증정포와 단백질바, 파로칩 등 후한 사은품 구성이 만족스러움
-뛰어난 가성비와 맛 — 할인가로 구매 시 매우 저렴하며 맛도 좋아 장기간 꾸준히 재구매함</t>
+          <t>속 편한 소화 개선 효과 — 섭취 후 더부룩함이 줄어들고 속이 편안해지는 효능이 탁월함.
+거부감 없는 고소한 맛 — 효소 특유의 거부감 없이 맛있게 먹을 수 있음.
+풍성한 증정품과 가성비 — 톡딜 이벤트 시 저렴하며 추가 증정품 구성이 매우 풍성함.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리가 덜 아프고 숙취 완화에 효과적임
-휴대 및 섭취의 용이성 — 스틱 액상 형태라 소지하기 좋고 거부감 없는 맛으로 물 없이 복용 가능함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 머리 아픔과 속 더부룩함이 크게 줄어듦.
+휴대가 간편한 액상 스틱 — 액상 스틱 형태로 물 없이도 바로 마실 수 있으며 휴대하기 편함.
+거부감 없는 상큼한 맛 — 환 제형과 달리 맛이 텁텁하지 않고 맛있어서 편하게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 뛰어난 맛 — 살이 부드럽고 퍽퍽하지 않으며 다양한 맛으로 구성되어 질리지 않음
-간편한 식단 관리 — 다이어트 식단 및 간식용으로 먹기 편리함</t>
+          <t>부드러운 식감과 우수한 맛 — 닭가슴살이 퍽퍽하지 않고 부드러우며 감칠맛이 뛰어남.
+다채롭고 질리지 않는 맛 — 옵션과 맛의 종류가 다채로워 매일 질리지 않고 먹을 수 있음.
+식단 관리용 간식 활용 — 칼로리 부담 없이 식단 관리나 간식용으로 활용하기 좋음.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>고소한 맛과 편안한 소화 — 미숫가루처럼 고소한 맛이 나며 식후 속을 편안하게 해줌
-정성스러운 선물 포장 — 패키지가 고급스럽고 견과류 바 등 사은품 혜택이 좋아 선물용으로 추천함</t>
+          <t>속 편한 소화 개선 효능 — 더부룩할 때 먹으면 속이 편안해지고 소화에 도움을 줌.
+고소한 미숫가루 풍미 — 텁텁함 없이 미숫가루나 곡물처럼 고소해서 먹기 부담 없음.
+고급 포장과 알찬 사은품 — 패키지가 고급스럽고 견과류 바 등 사은품 구성이 알참.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 조리 편의 — 닭가슴살이 촉촉하며 전자레인지로 간편하게 데워 먹기 좋음
-다양한 맛과 착한 가격 — 맛의 종류가 다양하여 질리지 않고 식단 관리할 수 있으며 가격이 저렴함</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살임에도 퍽퍽하지 않고 촉촉한 식감을 유지함.
+간편한 조리 및 활용성 — 전자레인지에 간편히 데워 식사 대용이나 반찬으로 먹기 좋음.
+다양하고 맛있는 양념 맛 — 떡볶이맛 등 다채로운 양념이 더해져 질리지 않고 식단 관리가 가능함.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>기획 굿즈와 알찬 구성 — 포토카드 및 엽서 굿즈와 증정 단백질바 구성이 훌륭함
-뛰어난 맛과 효과 — 쿠키앤크림, 소다 맛 등 맛이 우수하여 과식 후 먹기 좋음</t>
+          <t>포토카드 및 굿즈 구성 — 최애 멤버 포토카드와 엽서 등이 포함되어 만족도가 높음.
+맛있는 디저트 맛 효소 — 쿠키앤크림, 소다아이스크림 등 특색 있고 맛있는 맛으로 구성됨.
+풍성하고 알찬 추가 증정 — 함께 증정되는 단백질바 맛이 좋고 간식으로 활용하기 좋음.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 식감 — 계란 비린 맛이 전혀 없고 구운란처럼 맛과 식감이 뛰어남
-노른자 없는 단백질 섭취 — 흰자만 들어있어 퍽퍽하지 않고 껍질을 까는 번거로움 없이 간편하게 단백질 보충 가능함</t>
+          <t>노른자 없는 100% 흰자 — 노른자가 없어 퍽퍽하지 않고 칼로리 부담 없이 단백질만 챙길 수 있음.
+계란 비린내 없는 맛 — 비린 맛이 전혀 없고 구운란처럼 적당히 짭조름하여 맛있음.
+손쉬운 섭취의 간편식 — 껍질을 깔 필요가 없어 장소 구애 없이 전자레인지로 간편하게 먹음.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛과 가성비 — 떡볶이맛 등 다양한 맛으로 구성되어 가성비 있게 구매 가능함
-실용적인 사은품 가방 — 증정품으로 제공되는 보냉 가방의 디자인과 실용성이 우수함</t>
+          <t>맛있고 다채로운 양념 맛 — 떡볶이맛 등 양념이 다양하여 질리지 않고 맛있게 먹을 수 있음.
+실용적인 보냉 가방 증정 — 함께 제공되는 보냉가방의 디자인과 활용도가 뛰어남.</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 플리츠백 선물 포장이 예쁘고 고급스러워 개봉 시 기분이 좋음
-섭취 편의성과 맛 — 앰플 형태로 먹기 편하고 맛이 우수하여 피부 건강 관리에 용이함</t>
+          <t>다채로운 20종 상품 구성 — 식단이 질리지 않도록 다양한 닭가슴살 종류로 구성됨.
+부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함이 없이 부드럽고 촉촉하여 먹기 편함.
+전자레인지 전용 용기 제공 — 전용 용기가 포함되어 간편하게 조리하여 데워 먹기 좋음.</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 20종 구성 — 다양한 종류로 구성되어 질리지 않고 매일 다이어트 식단으로 즐기기 좋음
-촉촉한 식감과 편의성 — 닭가슴살이 부드럽고 촉촉하며 전자레인지 전용 용기를 제공해 편함</t>
+          <t>화려하고 고급스러운 포장 — 오간자 에디션 및 플리츠백 구성으로 선물의 격을 높여줌.
+맛있고 간편한 앰플 제형 — 비린 맛 없이 맛이 상큼하며 하루 한 병 간편하게 마실 수 있음.
+피부 수분 및 활력 개선 — 꾸준히 섭취 시 피부가 촉촉해지고 피로감이 완화되는 효과를 느낌.</t>
         </is>
       </c>
     </row>
@@ -4089,18 +4131,22 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 확인의 난해함 — 제공되는 기프티콘 수령 및 확인 방법에 대한 안내가 다소 미흡함.</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 박스 포장 상태 — 배송받은 포장 박스가 깨끗하지 않고 재활용된 느낌이 듦</t>
+          <t>단일 맛 구성의 아쉬움 — 맛 혼합 구성 옵션이 부족하고 배송 박스 위생 상태가 다소 아쉬움.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>누락 및 오배송 문제 — 상품 수량이 안 맞거나 사전에 없이 임의 대체 품목으로 배송됨
-강한 간과 해동 아쉬움 — 제품의 간이 세게 느껴지거나 배송 시 약간 녹아서 오는 점이 아쉬움</t>
+          <t>누락 오배송 시 느린 대응 — 구성품 수량이 맞지 않거나 대체품으로 누락되어 CS 응대가 지연됨.
+강한 간과 구성의 아쉬움 — 자극적인 양념 간이 강하고 가격 대비 가성비가 다소 저렴한 구성임.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4154,12 +4200,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4395,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4357,14 +4403,10 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
+          <t>베러핏 고단백 저당쉐이크 곡물맛</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>1,000원</t>
@@ -4372,34 +4414,30 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
-        </is>
-      </c>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031386196&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>589</v>
+        <v>936</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>적당한 크기와 무취 — 알약 크기가 적당하고 비린 냄새가 없어 먹기 편함</t>
+          <t>고소하고 담백한 곡물 맛 — 곡물 맛이 담백하고 고소하여 거부감 없이 맛있게 먹을 수 있음.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>꾸준한 복용 효과 기대 — 꾸준히 복용 시 몸이 좋아지는 체감을 기대할 수 있음</t>
+          <t>저당 고단백 한 끼 식사 — 당 부담은 낮추고 단백질이 든든하여 아침 식사 대용으로 적합함.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>불명확한 용법 설명 — 씹어 먹는지 물과 함께 먹는지 복용 방법이나 설명서 기재가 다소 혼란스러움</t>
+          <t>미세한 콩 특유의 잔향 — 목넘김 끝에 살짝 콩 특유의 향이나 냄새가 남는 편임.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -4408,7 +4446,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4416,49 +4454,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
+          <t>베러핏 고단백 저당쉐이크 흑임자맛</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602128&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/8husYxWOSsou1qKUi5IE613602128_00_018husYxWOSsou1qKUi5IE.jpg</t>
-        </is>
-      </c>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031386198&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1199</v>
+        <v>1074</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간식 같은 맛과 제형 — 맛있는 젤리 형태라 간식처럼 즐길 수 있어 알약을 잘 안 먹는 사람에게 적합함</t>
+          <t>진하고 고소한 흑임자 맛 — 물에만 타서 먹어도 흑임자 풍미가 진하며 많이 달지 않고 맛있음.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 비타민 충전 — 맛있고 편하게 하루 비타민을 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>훌륭한 가성비와 포만감 — 가격 대비 단백질 보충과 한 끼 식사 대용으로 부족함이 없음.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>편리한 휴대 및 목넘김 — 휴대성이 좋고 찬물에도 잘 풀려 깔끔하게 마실 수 있음.</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>영양제 특유의 향 — 약간의 영양제 특유의 향이 날 수 있음</t>
+          <t>잦은 품절로 인한 구매 난해 — 인기가 많아 재고 확보가 어렵고 구하기가 힘듦.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -4502,16 +4536,16 @@
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>7646</v>
+        <v>7654</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 30일분 구성으로 가격 부담이 적으며 성분 대비 가성비가 매우 훌륭함</t>
+          <t>우수한 가성비와 가격 — 합리적인 가격으로 꾸준히 부담 없이 구매하여 복용 가능함.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>작은 크기와 목넘김 — 알약 사이즈가 작아 목넘김이 편하고 섭취 후 피곤함이 덜함</t>
+          <t>작은 제형과 편한 목넘김 — 알약 크기가 작아서 목에 걸리는 느낌 없이 편하게 삼킬 수 있음.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4522,7 +4556,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4530,41 +4564,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 셀레늄 아연 30정 30일분</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000313&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>45</v>
+        <v>589</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>부담 없는 알약 크기 — 알약이 목으로 삼키기 쉬운 크기라 매일 섭취하기에 부담이 없음</t>
+          <t>비린내 없는 적당한 제형 — 오메가3 특유의 비린내가 없으며 알약 크기도 적당함.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>세포 보호 및 면역 관리 — 세포 보호와 면역력 유지를 위해 안심하고 구매하여 복용함</t>
+          <t>부담 없는 저렴한 가격 — 다이소 판매 제품답게 가격 부담 없이 오메가3를 복용해볼 수 있음.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>즉각적 체감 미흡 — 복용 초기에는 체감되는 효과를 바로 느끼기 어려울 수 있음</t>
+          <t>복용법 안내의 불명확함 — 물과 함께 삼키는지 씹어먹는지 섭취 가이드 설명이 불분명함.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -4608,27 +4650,31 @@
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>7144</v>
+        <v>7149</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>저렴한 가격과 디자인 — 3천원이라는 저렴한 가격으로 입문하기 좋으며 패키지 디자인도 우수함</t>
+          <t>가성비 및 깔끔한 디자인 — 가격이 저렴하고 용기 및 패키지 디자인이 예쁨.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>눈 떨림 방지 도움 — 눈 밑 떨림 현상 방지 및 수면 관리를 위해 부담 없이 챙겨 먹기 좋음</t>
+          <t>눈 떨림 증상 완화 효과 — 마그네슘 보충을 통해 눈 밑 떨림 증상 개선에 도움을 줌.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>잦은 품절로 인한 구매 난해 — 재고가 자주 부족하여 재입고 알림을 통해 겨우 구매해야 함.</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4636,7 +4682,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 프로폴리스 츄어블 30정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4646,44 +4692,48 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000150&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/Kpov6WvmW02F4pW9qB4z600000150_00_00Kpov6WvmW02F4pW9qB4z.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>5407</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>거부감 없는 편안한 맛 — 이상한 맛이 나지 않고 씹거나 물로 삼켜 먹기 적절함</t>
+          <t>식곤증 완화 및 혈당 케어 — 식사 후 피로감이나 식곤증이 줄어들어 만족도가 높음.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간절기 면역력 케어 — 환절기나 추운 날씨에 가볍게 면역력을 챙기기 가성비가 좋음</t>
+          <t>저렴한 가격과 높은 상비성 — 가격 부담이 적어 집에 상비해 두고 지속적으로 재구매함.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>체감 효과의 개인차 — 사람에 따라 효능을 즉각적으로 체감하지 못할 수 있음.</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4691,49 +4741,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624078&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/LCCefMiAcRv8JhM7m90p913624078_00_00LCCefMiAcRv8JhM7m90p.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>631</v>
+        <v>3005</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>톡톡 터지는 재밌는 맛 — 바나나킥 맛에 입안에서 톡톡 터지는 식감이 색다르고 맛있음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>수면 및 차분함에 도움 — 자기 전 복용 시 수면 유도가 잘 되고 마음이 차분해지는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>부담 없는 저렴한 가격 — 가격이 매우 저렴하여 다이어트 음료로 연하게 마시기 편함.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>약간의 멍함 및 개인차 — 섭취 후 다소 멍해지는 기분이 들 수 있고 효과에 개인차가 존재함</t>
+          <t>기대에 못 미치는 커피 맛 — 커피 풍미가 약하거나 입맛에 맞지 않아 맛에 대한 호불호가 큼.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -4742,7 +4788,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4750,12 +4796,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 아이라이트 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4765,34 +4811,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624076&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/zf0uM3McjshpycTXP0T2913624076_00_00zf0uM3McjshpycTXP0T2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>333</v>
+        <v>3807</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>눈 피로도 개선 체감 — 섭취 시 안 먹었을 때와 비교해 눈의 피로도가 확연히 줄어듦</t>
+          <t>3in1 복합 성분의 가성비 — 칼슘, 마그네슘, 비타민D를 합리적인 가격에 챙길 수 있음.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>맛있는 과립 제형 — 톡톡 튀는 맛이 있는 과립형이라 매일 챙겨 먹기 좋음</t>
+          <t>한 달 분량의 넉넉한 용량 — 한 달 동안 꾸준히 복용할 수 있도록 용량이 넉넉함.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>체감 효과의 부족 — 사람에 따라 별다른 효과를 느끼지 못할 수 있음</t>
+          <t>타 제품 대비 낮은 함량 — 시중의 고함량 영양제에 비해 일일 영양 성분 수치는 다소 낮음.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -4801,7 +4847,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4809,47 +4855,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 포스트바이오틱스 구미 7일분</t>
+          <t>대웅제약 콜라겐 60정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306207&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/EkCI0eksQMTFgi7Ae5eM032306207_00_01EkCI0eksQMTFgi7Ae5eM.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>381</v>
+        <v>1423</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>야쿠르트 맛의 구미 — 맛있는 야쿠르트 맛이라 간식처럼 부담 없이 먹기 좋음</t>
+          <t>1개월분 포장과 가성비 — 매우 저렴한 가격으로 한 달 치를 간편하게 챙길 수 있음.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성과 가성비 — 들고 다니기 좋고 가성비와 품질이 만족스러움</t>
+          <t>관절 및 연골 건강 케어 — 피부 외에도 관절과 연골 건강 보충용으로 복용하기 적합함.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>잦은 품절로 인한 구매 난해 — 재고 소진이 빨라 제때 구매하기가 어려움.</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -4864,51 +4914,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>751</v>
+        <v>1738</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 하루 2알 복용으로 화장실을 원활하게 가고 시원함을 체감함</t>
+          <t>100% 유기농 무첨가 성분 — 다른 첨가물 없이 순수 유기농 레몬즙이라 안심하고 섭취 가능함.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>음료 대비 편안한 맛 — 푸룬 음료보다 맛이 낫고 더부룩함이 적어 차량 등에서 간편하게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>호불호 갈리는 맛 — 입맛에 맞지 않아 맛 부분에서 아쉬움이 남을 수 있음</t>
-        </is>
-      </c>
+          <t>이지컷 개별 포장의 편의성 — 스틱 개별 포장에 이지컷이 적용되어 휴대가 편리하고 손쉽게 잘라 마심.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>다양한 요리 및 음료 활용 — 물에 타서 마시는 것 외에도 샐러드 드레싱이나 요리에 활용하기 좋음.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5023,24 +5073,24 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>마그네슘</t>
@@ -5048,22 +5098,22 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5078,22 +5128,18 @@
           <t>브랜드</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
@@ -5106,22 +5152,22 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>홀베리</t>
         </is>
       </c>
     </row>
@@ -5133,24 +5179,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>베러핏 고단백 저당쉐이크 곡물맛</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>베러핏 고단백 저당쉐이크 흑임자맛</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 셀레늄 아연 30정 30일분</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>대웅제약 마그네슘 30정 30일분</t>
@@ -5158,27 +5204,27 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 프로폴리스 츄어블 30정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 아이라이트 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 포스트바이오틱스 구미 7일분</t>
+          <t>대웅제약 콜라겐 60정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5235,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5207,16 +5253,16 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5226,37 +5272,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>936</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1074</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7654</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>589</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>1199</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>7646</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>45</v>
-      </c>
       <c r="G7" s="3" t="n">
-        <v>7144</v>
+        <v>7149</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>788</v>
+        <v>5407</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>631</v>
+        <v>3005</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>333</v>
+        <v>3807</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>381</v>
+        <v>1423</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5264,62 +5310,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>적당한 크기와 무취 — 알약 크기가 적당하고 비린 냄새가 없어 먹기 편함
-꾸준한 복용 효과 기대 — 꾸준히 복용 시 몸이 좋아지는 체감을 기대할 수 있음</t>
+          <t>고소하고 담백한 곡물 맛 — 곡물 맛이 담백하고 고소하여 거부감 없이 맛있게 먹을 수 있음.
+저당 고단백 한 끼 식사 — 당 부담은 낮추고 단백질이 든든하여 아침 식사 대용으로 적합함.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간식 같은 맛과 제형 — 맛있는 젤리 형태라 간식처럼 즐길 수 있어 알약을 잘 안 먹는 사람에게 적합함
-간편한 비타민 충전 — 맛있고 편하게 하루 비타민을 챙겨 먹기 좋음</t>
+          <t>진하고 고소한 흑임자 맛 — 물에만 타서 먹어도 흑임자 풍미가 진하며 많이 달지 않고 맛있음.
+훌륭한 가성비와 포만감 — 가격 대비 단백질 보충과 한 끼 식사 대용으로 부족함이 없음.
+편리한 휴대 및 목넘김 — 휴대성이 좋고 찬물에도 잘 풀려 깔끔하게 마실 수 있음.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 30일분 구성으로 가격 부담이 적으며 성분 대비 가성비가 매우 훌륭함
-작은 크기와 목넘김 — 알약 사이즈가 작아 목넘김이 편하고 섭취 후 피곤함이 덜함</t>
+          <t>우수한 가성비와 가격 — 합리적인 가격으로 꾸준히 부담 없이 구매하여 복용 가능함.
+작은 제형과 편한 목넘김 — 알약 크기가 작아서 목에 걸리는 느낌 없이 편하게 삼킬 수 있음.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 알약 크기 — 알약이 목으로 삼키기 쉬운 크기라 매일 섭취하기에 부담이 없음
-세포 보호 및 면역 관리 — 세포 보호와 면역력 유지를 위해 안심하고 구매하여 복용함</t>
+          <t>비린내 없는 적당한 제형 — 오메가3 특유의 비린내가 없으며 알약 크기도 적당함.
+부담 없는 저렴한 가격 — 다이소 판매 제품답게 가격 부담 없이 오메가3를 복용해볼 수 있음.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 디자인 — 3천원이라는 저렴한 가격으로 입문하기 좋으며 패키지 디자인도 우수함
-눈 떨림 방지 도움 — 눈 밑 떨림 현상 방지 및 수면 관리를 위해 부담 없이 챙겨 먹기 좋음</t>
+          <t>가성비 및 깔끔한 디자인 — 가격이 저렴하고 용기 및 패키지 디자인이 예쁨.
+눈 떨림 증상 완화 효과 — 마그네슘 보충을 통해 눈 밑 떨림 증상 개선에 도움을 줌.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 편안한 맛 — 이상한 맛이 나지 않고 씹거나 물로 삼켜 먹기 적절함
-간절기 면역력 케어 — 환절기나 추운 날씨에 가볍게 면역력을 챙기기 가성비가 좋음</t>
+          <t>식곤증 완화 및 혈당 케어 — 식사 후 피로감이나 식곤증이 줄어들어 만족도가 높음.
+저렴한 가격과 높은 상비성 — 가격 부담이 적어 집에 상비해 두고 지속적으로 재구매함.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>톡톡 터지는 재밌는 맛 — 바나나킥 맛에 입안에서 톡톡 터지는 식감이 색다르고 맛있음
-수면 및 차분함에 도움 — 자기 전 복용 시 수면 유도가 잘 되고 마음이 차분해지는 느낌을 받음</t>
+          <t>부담 없는 저렴한 가격 — 가격이 매우 저렴하여 다이어트 음료로 연하게 마시기 편함.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>눈 피로도 개선 체감 — 섭취 시 안 먹었을 때와 비교해 눈의 피로도가 확연히 줄어듦
-맛있는 과립 제형 — 톡톡 튀는 맛이 있는 과립형이라 매일 챙겨 먹기 좋음</t>
+          <t>3in1 복합 성분의 가성비 — 칼슘, 마그네슘, 비타민D를 합리적인 가격에 챙길 수 있음.
+한 달 분량의 넉넉한 용량 — 한 달 동안 꾸준히 복용할 수 있도록 용량이 넉넉함.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>야쿠르트 맛의 구미 — 맛있는 야쿠르트 맛이라 간식처럼 부담 없이 먹기 좋음
-뛰어난 휴대성과 가성비 — 들고 다니기 좋고 가성비와 품질이 만족스러움</t>
+          <t>1개월분 포장과 가성비 — 매우 저렴한 가격으로 한 달 치를 간편하게 챙길 수 있음.
+관절 및 연골 건강 케어 — 피부 외에도 관절과 연골 건강 보충용으로 복용하기 적합함.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 하루 2알 복용으로 화장실을 원활하게 가고 시원함을 체감함
-음료 대비 편안한 맛 — 푸룬 음료보다 맛이 낫고 더부룩함이 적어 차량 등에서 간편하게 먹기 좋음</t>
+          <t>100% 유기농 무첨가 성분 — 다른 첨가물 없이 순수 유기농 레몬즙이라 안심하고 섭취 가능함.
+이지컷 개별 포장의 편의성 — 스틱 개별 포장에 이지컷이 적용되어 휴대가 편리하고 손쉽게 잘라 마심.
+다양한 요리 및 음료 활용 — 물에 타서 마시는 것 외에도 샐러드 드레싱이나 요리에 활용하기 좋음.</t>
         </is>
       </c>
     </row>
@@ -5331,38 +5378,46 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>불명확한 용법 설명 — 씹어 먹는지 물과 함께 먹는지 복용 방법이나 설명서 기재가 다소 혼란스러움</t>
+          <t>미세한 콩 특유의 잔향 — 목넘김 끝에 살짝 콩 특유의 향이나 냄새가 남는 편임.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>영양제 특유의 향 — 약간의 영양제 특유의 향이 날 수 있음</t>
+          <t>잦은 품절로 인한 구매 난해 — 인기가 많아 재고 확보가 어렵고 구하기가 힘듦.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>즉각적 체감 미흡 — 복용 초기에는 체감되는 효과를 바로 느끼기 어려울 수 있음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+          <t>복용법 안내의 불명확함 — 물과 함께 삼키는지 씹어먹는지 섭취 가이드 설명이 불분명함.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>잦은 품절로 인한 구매 난해 — 재고가 자주 부족하여 재입고 알림을 통해 겨우 구매해야 함.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>체감 효과의 개인차 — 사람에 따라 효능을 즉각적으로 체감하지 못할 수 있음.</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>약간의 멍함 및 개인차 — 섭취 후 다소 멍해지는 기분이 들 수 있고 효과에 개인차가 존재함</t>
+          <t>기대에 못 미치는 커피 맛 — 커피 풍미가 약하거나 입맛에 맞지 않아 맛에 대한 호불호가 큼.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과의 부족 — 사람에 따라 별다른 효과를 느끼지 못할 수 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>호불호 갈리는 맛 — 입맛에 맞지 않아 맛 부분에서 아쉬움이 남을 수 있음</t>
-        </is>
-      </c>
+          <t>타 제품 대비 낮은 함량 — 시중의 고함량 영양제에 비해 일일 영양 성분 수치는 다소 낮음.</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>잦은 품절로 인한 구매 난해 — 재고 소진이 빨라 제때 구매하기가 어려움.</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5377,47 +5432,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5542,16 +5597,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5561,16 +5616,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5580,22 +5635,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5605,16 +5660,16 @@
         <v>6.7</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5633,7 +5688,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5643,16 +5698,16 @@
         <v>3.3</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5671,7 +5726,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5690,7 +5745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5703,6 +5758,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
       </c>
     </row>
